--- a/data/trans_camb/P1802_2016_2023-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1802_2016_2023-Estudios-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,26</t>
+          <t>1,64</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-2,86</t>
+          <t>-3,06</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-1,0</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 7,68</t>
+          <t>-2,09; 5,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 0,33</t>
+          <t>-6,7; 0,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 2,34</t>
+          <t>-3,6; 1,51</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-12,26%</t>
+          <t>-13,13%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-1,01%</t>
+          <t>-4,88%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 52,12</t>
+          <t>-11,6; 39,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 1,43</t>
+          <t>-26,16; 1,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 12,63</t>
+          <t>-16,55; 7,79</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,56</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-2,35</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>0,56</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 34,8</t>
+          <t>-1,23; 2,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 0,59</t>
+          <t>-1,85; 2,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 18,02</t>
+          <t>-1,08; 2,22</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-13,53%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 247,76</t>
+          <t>-8,38; 22,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,47; 3,23</t>
+          <t>-9,76; 15,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 120,07</t>
+          <t>-6,52; 15,41</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,91</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,44</t>
+          <t>3,98</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>2,68</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,93</t>
+          <t>-3,08; 5,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 8,6</t>
+          <t>-0,1; 8,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,3</t>
+          <t>-0,35; 5,58</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 53,03</t>
+          <t>-19,54; 47,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,23; 61,4</t>
+          <t>-0,49; 61,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 47,58</t>
+          <t>-2,32; 43,27</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>0,36</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 24,82</t>
+          <t>-0,83; 2,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 0,52</t>
+          <t>-2,0; 1,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 13,93</t>
+          <t>-0,88; 1,52</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-8,95%</t>
+          <t>-0,75%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,43; 176,84</t>
+          <t>-5,69; 19,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 2,87</t>
+          <t>-10,1; 9,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 84,15</t>
+          <t>-5,06; 9,43</t>
         </is>
       </c>
     </row>
